--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_Morte_999.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_Morte_999.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1246" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1253" uniqueCount="192">
   <si>
     <t>Sezione</t>
   </si>
@@ -132,6 +132,12 @@
   </si>
   <si>
     <t>testoDataPresuntaMorte</t>
+  </si>
+  <si>
+    <t>Data rinvenimento cadavere</t>
+  </si>
+  <si>
+    <t>dataRinvenimentoCadavere</t>
   </si>
   <si>
     <t>Luogo</t>
@@ -640,7 +646,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H178"/>
+  <dimension ref="A1:H179"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="26.12890625" customWidth="true" bestFit="true"/>
@@ -1005,7 +1011,7 @@
         <v>42</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>28</v>
@@ -1051,7 +1057,7 @@
         <v>46</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>28</v>
@@ -1183,19 +1189,19 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>10</v>
@@ -1206,7 +1212,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>61</v>
@@ -1229,7 +1235,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>63</v>
@@ -1252,7 +1258,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>65</v>
@@ -1275,7 +1281,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>67</v>
@@ -1298,7 +1304,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>69</v>
@@ -1321,7 +1327,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>71</v>
@@ -1344,19 +1350,19 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>10</v>
@@ -1367,16 +1373,16 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>78</v>
@@ -1390,16 +1396,16 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>80</v>
@@ -1413,16 +1419,16 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>82</v>
@@ -1436,16 +1442,16 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>84</v>
@@ -1459,7 +1465,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>85</v>
@@ -1468,7 +1474,7 @@
         <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>86</v>
@@ -1482,16 +1488,16 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>88</v>
@@ -1505,7 +1511,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>89</v>
@@ -1514,7 +1520,7 @@
         <v>13</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>90</v>
@@ -1528,7 +1534,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>91</v>
@@ -1537,7 +1543,7 @@
         <v>13</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>92</v>
@@ -1551,16 +1557,16 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>93</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>94</v>
@@ -1574,7 +1580,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>95</v>
@@ -1583,7 +1589,7 @@
         <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>96</v>
@@ -1597,7 +1603,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>97</v>
@@ -1606,7 +1612,7 @@
         <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>98</v>
@@ -1620,7 +1626,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>99</v>
@@ -1629,7 +1635,7 @@
         <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>100</v>
@@ -1643,19 +1649,19 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>54</v>
+        <v>101</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>10</v>
@@ -1666,16 +1672,16 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>103</v>
@@ -1689,7 +1695,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>104</v>
@@ -1698,7 +1704,7 @@
         <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>105</v>
@@ -1712,7 +1718,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>106</v>
@@ -1721,7 +1727,7 @@
         <v>9</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>107</v>
@@ -1735,7 +1741,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>108</v>
@@ -1744,7 +1750,7 @@
         <v>9</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>109</v>
@@ -1758,7 +1764,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>110</v>
@@ -1767,7 +1773,7 @@
         <v>9</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>111</v>
@@ -1781,7 +1787,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>112</v>
@@ -1790,7 +1796,7 @@
         <v>9</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>113</v>
@@ -1804,7 +1810,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>114</v>
@@ -1813,7 +1819,7 @@
         <v>9</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>115</v>
@@ -1827,7 +1833,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>116</v>
@@ -1836,7 +1842,7 @@
         <v>9</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>117</v>
@@ -1850,7 +1856,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>118</v>
@@ -1859,7 +1865,7 @@
         <v>9</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>119</v>
@@ -1873,7 +1879,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>120</v>
@@ -1882,7 +1888,7 @@
         <v>9</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>121</v>
@@ -1896,7 +1902,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>122</v>
@@ -1905,7 +1911,7 @@
         <v>9</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>123</v>
@@ -1919,7 +1925,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>124</v>
@@ -1928,7 +1934,7 @@
         <v>9</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>125</v>
@@ -1942,7 +1948,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>126</v>
@@ -1951,7 +1957,7 @@
         <v>9</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>127</v>
@@ -1965,7 +1971,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>128</v>
@@ -1974,7 +1980,7 @@
         <v>9</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>129</v>
@@ -1988,7 +1994,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>130</v>
@@ -1997,7 +2003,7 @@
         <v>9</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>131</v>
@@ -2011,7 +2017,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>132</v>
@@ -2020,7 +2026,7 @@
         <v>9</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>133</v>
@@ -2034,7 +2040,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>134</v>
@@ -2043,7 +2049,7 @@
         <v>9</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>135</v>
@@ -2057,7 +2063,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>136</v>
@@ -2066,7 +2072,7 @@
         <v>9</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>137</v>
@@ -2080,39 +2086,39 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B63" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B63" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="C63" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D63" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E63" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="E63" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F63" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>140</v>
+        <v>19</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>78</v>
@@ -2121,21 +2127,21 @@
         <v>10</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>80</v>
@@ -2144,21 +2150,21 @@
         <v>10</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>82</v>
@@ -2167,21 +2173,21 @@
         <v>10</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>84</v>
@@ -2190,12 +2196,12 @@
         <v>10</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>85</v>
@@ -2204,7 +2210,7 @@
         <v>9</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>86</v>
@@ -2213,21 +2219,21 @@
         <v>10</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>88</v>
@@ -2236,12 +2242,12 @@
         <v>10</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>89</v>
@@ -2250,7 +2256,7 @@
         <v>13</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>90</v>
@@ -2259,12 +2265,12 @@
         <v>10</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>91</v>
@@ -2273,7 +2279,7 @@
         <v>13</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>92</v>
@@ -2282,21 +2288,21 @@
         <v>10</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>93</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>94</v>
@@ -2305,12 +2311,12 @@
         <v>10</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>95</v>
@@ -2319,7 +2325,7 @@
         <v>9</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>96</v>
@@ -2328,12 +2334,12 @@
         <v>10</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>97</v>
@@ -2342,7 +2348,7 @@
         <v>9</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>98</v>
@@ -2351,12 +2357,12 @@
         <v>10</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>99</v>
@@ -2365,7 +2371,7 @@
         <v>9</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>100</v>
@@ -2374,44 +2380,44 @@
         <v>10</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>54</v>
+        <v>101</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>103</v>
@@ -2420,12 +2426,12 @@
         <v>10</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>104</v>
@@ -2434,7 +2440,7 @@
         <v>13</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>105</v>
@@ -2443,21 +2449,21 @@
         <v>10</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>106</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>107</v>
@@ -2466,12 +2472,12 @@
         <v>10</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>108</v>
@@ -2480,7 +2486,7 @@
         <v>9</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>109</v>
@@ -2489,12 +2495,12 @@
         <v>10</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>110</v>
@@ -2503,7 +2509,7 @@
         <v>9</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>111</v>
@@ -2512,12 +2518,12 @@
         <v>10</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>112</v>
@@ -2526,7 +2532,7 @@
         <v>9</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>113</v>
@@ -2535,12 +2541,12 @@
         <v>10</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>114</v>
@@ -2549,7 +2555,7 @@
         <v>9</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>115</v>
@@ -2558,12 +2564,12 @@
         <v>10</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>116</v>
@@ -2572,7 +2578,7 @@
         <v>9</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>117</v>
@@ -2581,12 +2587,12 @@
         <v>10</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>118</v>
@@ -2595,7 +2601,7 @@
         <v>9</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>119</v>
@@ -2604,12 +2610,12 @@
         <v>10</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>120</v>
@@ -2618,7 +2624,7 @@
         <v>9</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>121</v>
@@ -2627,12 +2633,12 @@
         <v>10</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>122</v>
@@ -2641,7 +2647,7 @@
         <v>9</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>123</v>
@@ -2650,21 +2656,21 @@
         <v>10</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>124</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>125</v>
@@ -2673,12 +2679,12 @@
         <v>10</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>126</v>
@@ -2687,7 +2693,7 @@
         <v>13</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>127</v>
@@ -2696,12 +2702,12 @@
         <v>10</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>128</v>
@@ -2710,7 +2716,7 @@
         <v>13</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>129</v>
@@ -2719,44 +2725,44 @@
         <v>10</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D91" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B91" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>143</v>
-      </c>
       <c r="E91" s="2" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B92" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D92" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>143</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>146</v>
@@ -2765,12 +2771,12 @@
         <v>10</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>147</v>
@@ -2779,7 +2785,7 @@
         <v>13</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>148</v>
@@ -2788,12 +2794,12 @@
         <v>10</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>149</v>
@@ -2802,7 +2808,7 @@
         <v>13</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>150</v>
@@ -2811,12 +2817,12 @@
         <v>10</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>151</v>
@@ -2825,7 +2831,7 @@
         <v>13</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>152</v>
@@ -2834,12 +2840,12 @@
         <v>10</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>153</v>
@@ -2848,7 +2854,7 @@
         <v>13</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>154</v>
@@ -2857,12 +2863,12 @@
         <v>10</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>155</v>
@@ -2871,90 +2877,90 @@
         <v>13</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>18</v>
+        <v>156</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>157</v>
+        <v>18</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>158</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>21</v>
+        <v>159</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>160</v>
+        <v>21</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>161</v>
@@ -2963,7 +2969,7 @@
         <v>9</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>162</v>
@@ -2972,12 +2978,12 @@
         <v>10</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>163</v>
@@ -2986,7 +2992,7 @@
         <v>9</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>164</v>
@@ -2995,12 +3001,12 @@
         <v>10</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>165</v>
@@ -3009,7 +3015,7 @@
         <v>9</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>166</v>
@@ -3018,44 +3024,44 @@
         <v>10</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B104" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="B104" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="C104" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D104" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E104" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="E104" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F104" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>169</v>
+        <v>142</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>78</v>
@@ -3064,12 +3070,12 @@
         <v>10</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>79</v>
@@ -3078,7 +3084,7 @@
         <v>9</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>80</v>
@@ -3087,12 +3093,12 @@
         <v>10</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>81</v>
@@ -3101,7 +3107,7 @@
         <v>9</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>82</v>
@@ -3110,12 +3116,12 @@
         <v>10</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>83</v>
@@ -3124,7 +3130,7 @@
         <v>9</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>84</v>
@@ -3133,12 +3139,12 @@
         <v>10</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>85</v>
@@ -3147,7 +3153,7 @@
         <v>9</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>86</v>
@@ -3156,12 +3162,12 @@
         <v>10</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>87</v>
@@ -3170,7 +3176,7 @@
         <v>9</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>88</v>
@@ -3179,12 +3185,12 @@
         <v>10</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>89</v>
@@ -3193,7 +3199,7 @@
         <v>9</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>90</v>
@@ -3202,12 +3208,12 @@
         <v>10</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>91</v>
@@ -3216,7 +3222,7 @@
         <v>9</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>92</v>
@@ -3225,12 +3231,12 @@
         <v>10</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>93</v>
@@ -3239,7 +3245,7 @@
         <v>9</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>94</v>
@@ -3248,12 +3254,12 @@
         <v>10</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>95</v>
@@ -3262,7 +3268,7 @@
         <v>9</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>96</v>
@@ -3271,12 +3277,12 @@
         <v>10</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>97</v>
@@ -3285,7 +3291,7 @@
         <v>9</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>98</v>
@@ -3294,12 +3300,12 @@
         <v>10</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>99</v>
@@ -3308,7 +3314,7 @@
         <v>9</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>100</v>
@@ -3317,44 +3323,44 @@
         <v>10</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>54</v>
+        <v>101</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>103</v>
@@ -3363,12 +3369,12 @@
         <v>10</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>104</v>
@@ -3377,7 +3383,7 @@
         <v>9</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>105</v>
@@ -3386,12 +3392,12 @@
         <v>10</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>106</v>
@@ -3400,7 +3406,7 @@
         <v>9</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>107</v>
@@ -3409,12 +3415,12 @@
         <v>10</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>108</v>
@@ -3423,7 +3429,7 @@
         <v>9</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>109</v>
@@ -3432,12 +3438,12 @@
         <v>10</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>110</v>
@@ -3446,7 +3452,7 @@
         <v>9</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>111</v>
@@ -3455,12 +3461,12 @@
         <v>10</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>112</v>
@@ -3469,7 +3475,7 @@
         <v>9</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>113</v>
@@ -3478,12 +3484,12 @@
         <v>10</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>114</v>
@@ -3492,7 +3498,7 @@
         <v>9</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>115</v>
@@ -3501,12 +3507,12 @@
         <v>10</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>116</v>
@@ -3515,7 +3521,7 @@
         <v>9</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>117</v>
@@ -3524,12 +3530,12 @@
         <v>10</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>118</v>
@@ -3538,7 +3544,7 @@
         <v>9</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>119</v>
@@ -3547,12 +3553,12 @@
         <v>10</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>120</v>
@@ -3561,7 +3567,7 @@
         <v>9</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>121</v>
@@ -3570,12 +3576,12 @@
         <v>10</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>122</v>
@@ -3584,7 +3590,7 @@
         <v>9</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>123</v>
@@ -3593,12 +3599,12 @@
         <v>10</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>124</v>
@@ -3607,7 +3613,7 @@
         <v>9</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>125</v>
@@ -3616,12 +3622,12 @@
         <v>10</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>126</v>
@@ -3630,7 +3636,7 @@
         <v>9</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>127</v>
@@ -3639,21 +3645,21 @@
         <v>10</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>170</v>
+        <v>128</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>129</v>
@@ -3662,44 +3668,44 @@
         <v>10</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F132" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G132" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="B132" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C132" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D132" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="E132" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F132" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G132" s="2" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>78</v>
@@ -3708,12 +3714,12 @@
         <v>10</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>79</v>
@@ -3722,7 +3728,7 @@
         <v>9</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>80</v>
@@ -3731,12 +3737,12 @@
         <v>10</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>81</v>
@@ -3745,7 +3751,7 @@
         <v>9</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>82</v>
@@ -3754,12 +3760,12 @@
         <v>10</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>83</v>
@@ -3768,7 +3774,7 @@
         <v>9</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>84</v>
@@ -3777,12 +3783,12 @@
         <v>10</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>85</v>
@@ -3791,7 +3797,7 @@
         <v>9</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>86</v>
@@ -3800,12 +3806,12 @@
         <v>10</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>87</v>
@@ -3814,7 +3820,7 @@
         <v>9</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>88</v>
@@ -3823,12 +3829,12 @@
         <v>10</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>89</v>
@@ -3837,7 +3843,7 @@
         <v>9</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>90</v>
@@ -3846,12 +3852,12 @@
         <v>10</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>91</v>
@@ -3860,7 +3866,7 @@
         <v>9</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>92</v>
@@ -3869,12 +3875,12 @@
         <v>10</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>93</v>
@@ -3883,7 +3889,7 @@
         <v>9</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>94</v>
@@ -3892,12 +3898,12 @@
         <v>10</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>95</v>
@@ -3906,7 +3912,7 @@
         <v>9</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>96</v>
@@ -3915,12 +3921,12 @@
         <v>10</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>97</v>
@@ -3929,7 +3935,7 @@
         <v>9</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>98</v>
@@ -3938,12 +3944,12 @@
         <v>10</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>99</v>
@@ -3952,7 +3958,7 @@
         <v>9</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>100</v>
@@ -3961,44 +3967,44 @@
         <v>10</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>54</v>
+        <v>101</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F145" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>103</v>
@@ -4007,12 +4013,12 @@
         <v>10</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>104</v>
@@ -4021,7 +4027,7 @@
         <v>9</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>105</v>
@@ -4030,12 +4036,12 @@
         <v>10</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>106</v>
@@ -4044,7 +4050,7 @@
         <v>9</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>107</v>
@@ -4053,12 +4059,12 @@
         <v>10</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>108</v>
@@ -4067,7 +4073,7 @@
         <v>9</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>109</v>
@@ -4076,12 +4082,12 @@
         <v>10</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>110</v>
@@ -4090,7 +4096,7 @@
         <v>9</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>111</v>
@@ -4099,12 +4105,12 @@
         <v>10</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>112</v>
@@ -4113,7 +4119,7 @@
         <v>9</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>113</v>
@@ -4122,12 +4128,12 @@
         <v>10</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>114</v>
@@ -4136,7 +4142,7 @@
         <v>9</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>115</v>
@@ -4145,12 +4151,12 @@
         <v>10</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B153" s="2" t="s">
         <v>116</v>
@@ -4159,7 +4165,7 @@
         <v>9</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>117</v>
@@ -4168,12 +4174,12 @@
         <v>10</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>118</v>
@@ -4182,7 +4188,7 @@
         <v>9</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>119</v>
@@ -4191,12 +4197,12 @@
         <v>10</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>120</v>
@@ -4205,7 +4211,7 @@
         <v>9</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>121</v>
@@ -4214,12 +4220,12 @@
         <v>10</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>122</v>
@@ -4228,7 +4234,7 @@
         <v>9</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>123</v>
@@ -4237,12 +4243,12 @@
         <v>10</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>124</v>
@@ -4251,7 +4257,7 @@
         <v>9</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>125</v>
@@ -4260,12 +4266,12 @@
         <v>10</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>126</v>
@@ -4274,7 +4280,7 @@
         <v>9</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>127</v>
@@ -4283,21 +4289,21 @@
         <v>10</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>170</v>
+        <v>128</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>129</v>
@@ -4306,7 +4312,7 @@
         <v>10</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="160">
@@ -4314,22 +4320,22 @@
         <v>173</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>17</v>
+        <v>170</v>
       </c>
       <c r="E160" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F160" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G160" s="2" t="s">
         <v>174</v>
-      </c>
-      <c r="F160" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G160" s="2" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="161">
@@ -4337,16 +4343,16 @@
         <v>175</v>
       </c>
       <c r="B161" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E161" s="2" t="s">
         <v>176</v>
-      </c>
-      <c r="C161" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D161" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E161" s="2" t="s">
-        <v>177</v>
       </c>
       <c r="F161" s="2" t="s">
         <v>10</v>
@@ -4357,7 +4363,7 @@
     </row>
     <row r="162">
       <c r="A162" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>178</v>
@@ -4366,7 +4372,7 @@
         <v>9</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>179</v>
@@ -4380,39 +4386,39 @@
     </row>
     <row r="163">
       <c r="A163" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B163" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="B163" s="2" t="s">
-        <v>142</v>
-      </c>
       <c r="C163" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D163" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E163" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="E163" s="2" t="s">
-        <v>144</v>
-      </c>
       <c r="F163" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>140</v>
+        <v>19</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>146</v>
@@ -4421,12 +4427,12 @@
         <v>10</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B165" s="2" t="s">
         <v>147</v>
@@ -4435,7 +4441,7 @@
         <v>9</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>148</v>
@@ -4444,12 +4450,12 @@
         <v>10</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>149</v>
@@ -4458,7 +4464,7 @@
         <v>9</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>150</v>
@@ -4467,12 +4473,12 @@
         <v>10</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>151</v>
@@ -4481,7 +4487,7 @@
         <v>9</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>152</v>
@@ -4490,12 +4496,12 @@
         <v>10</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B168" s="2" t="s">
         <v>153</v>
@@ -4504,7 +4510,7 @@
         <v>9</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>154</v>
@@ -4513,12 +4519,12 @@
         <v>10</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B169" s="2" t="s">
         <v>155</v>
@@ -4527,44 +4533,44 @@
         <v>9</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>18</v>
+        <v>156</v>
       </c>
       <c r="F169" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>157</v>
+        <v>18</v>
       </c>
       <c r="F170" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B171" s="2" t="s">
         <v>158</v>
@@ -4573,44 +4579,44 @@
         <v>9</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>21</v>
+        <v>159</v>
       </c>
       <c r="F171" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>160</v>
+        <v>21</v>
       </c>
       <c r="F172" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B173" s="2" t="s">
         <v>161</v>
@@ -4619,7 +4625,7 @@
         <v>9</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>162</v>
@@ -4628,12 +4634,12 @@
         <v>10</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B174" s="2" t="s">
         <v>163</v>
@@ -4642,7 +4648,7 @@
         <v>9</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>164</v>
@@ -4651,12 +4657,12 @@
         <v>10</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B175" s="2" t="s">
         <v>165</v>
@@ -4665,7 +4671,7 @@
         <v>9</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>166</v>
@@ -4674,7 +4680,7 @@
         <v>10</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="176">
@@ -4682,36 +4688,36 @@
         <v>182</v>
       </c>
       <c r="B176" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D176" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C176" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D176" s="2" t="s">
-        <v>184</v>
-      </c>
       <c r="E176" s="2" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="F176" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>19</v>
+        <v>142</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B177" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D177" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="C177" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D177" s="2" t="s">
-        <v>184</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>187</v>
@@ -4725,7 +4731,7 @@
     </row>
     <row r="178">
       <c r="A178" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B178" s="2" t="s">
         <v>188</v>
@@ -4734,7 +4740,7 @@
         <v>9</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E178" s="2" t="s">
         <v>189</v>
@@ -4743,6 +4749,29 @@
         <v>10</v>
       </c>
       <c r="G178" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E179" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="F179" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G179" s="2" t="s">
         <v>19</v>
       </c>
     </row>

--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_Morte_999.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_Morte_999.xlsx
@@ -2874,7 +2874,7 @@
         <v>155</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>145</v>
